--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-03-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-03-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1D7829-A682-4799-A43C-09836BF7B3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C211B49-32CB-4251-B06B-7D1A3F1D65AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
